--- a/docs/weekly-mini-projects/weekly-mini-project-02/evaluation/Weekly_Mini_Project_02_Team_4_Leader_Evaluation.xlsx
+++ b/docs/weekly-mini-projects/weekly-mini-project-02/evaluation/Weekly_Mini_Project_02_Team_4_Leader_Evaluation.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nawarhisso/Documents/Training/BootCamp/repositories/b4f-cohort8-salamiyah-react-node-bootcamp-2026/docs/Weekly Mini Projects/weekly-mini-project-01/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Allaith 3Issa\Desktop\B4F-BootCamp\b4f-cohort8-salamiyah-next-nest-bootcamp-2026\docs\weekly-mini-projects\weekly-mini-project-02\evaluation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C93E6B9-15EC-6942-A139-EFA1D0FA24FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20F4125C-4D00-482F-A8A7-B716A1B4694B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Evaluation" sheetId="1" r:id="rId1"/>
     <sheet name="Criteria Guide" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="79">
   <si>
     <t>Weekly Mini Project 02 — Leader Evaluation of Team Members</t>
   </si>
@@ -228,6 +228,48 @@
   </si>
   <si>
     <t>Excellent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">build event page, filters and past event section </t>
+  </si>
+  <si>
+    <t>build event form and event details page</t>
+  </si>
+  <si>
+    <t>build booking module</t>
+  </si>
+  <si>
+    <t>build event module and common folder(filters and helpers), sotre and recap all backend code</t>
+  </si>
+  <si>
+    <t>build manage booking section</t>
+  </si>
+  <si>
+    <t xml:space="preserve">He did everything very well </t>
+  </si>
+  <si>
+    <t xml:space="preserve">He did his tasks </t>
+  </si>
+  <si>
+    <t>working on variables, arrays and functions name</t>
+  </si>
+  <si>
+    <t>working on a better structure and segmentation for the frontend architecture</t>
+  </si>
+  <si>
+    <t>to have more confidence in his abilities</t>
+  </si>
+  <si>
+    <t>\to treat the project as if it were his own and to learn more about it</t>
+  </si>
+  <si>
+    <t>She is a genius in the frontend</t>
+  </si>
+  <si>
+    <t>he is smart and he has a logical thinking but he doesn’t know how to utilize it</t>
+  </si>
+  <si>
+    <t>he is hard worker</t>
   </si>
 </sst>
 </file>
@@ -792,16 +834,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:V16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.5" customWidth="1"/>
+    <col min="1" max="1" width="8.44140625" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="17" width="13" customWidth="1"/>
     <col min="18" max="18" width="11" customWidth="1"/>
     <col min="19" max="22" width="38" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
@@ -827,7 +869,7 @@
       <c r="U1" s="23"/>
       <c r="V1" s="23"/>
     </row>
-    <row r="2" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
@@ -853,7 +895,7 @@
       <c r="U2" s="23"/>
       <c r="V2" s="23"/>
     </row>
-    <row r="3" spans="1:22" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:22" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
         <v>2</v>
       </c>
@@ -879,7 +921,7 @@
       <c r="U3" s="23"/>
       <c r="V3" s="23"/>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -889,7 +931,7 @@
       <c r="C4" s="25"/>
       <c r="D4" s="26"/>
     </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -899,7 +941,7 @@
       <c r="C5" s="25"/>
       <c r="D5" s="26"/>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -909,12 +951,12 @@
       <c r="C6" s="25"/>
       <c r="D6" s="26"/>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="29" t="s">
         <v>10</v>
       </c>
@@ -940,7 +982,7 @@
       <c r="U8" s="23"/>
       <c r="V8" s="23"/>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A10" s="27" t="s">
         <v>11</v>
       </c>
@@ -972,7 +1014,7 @@
       <c r="U10" s="25"/>
       <c r="V10" s="26"/>
     </row>
-    <row r="11" spans="1:22" ht="62" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" ht="61.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>15</v>
       </c>
@@ -1040,159 +1082,343 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:22" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:22" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="6">
         <v>1</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="8"/>
-      <c r="M12" s="8"/>
-      <c r="N12" s="8"/>
-      <c r="O12" s="8"/>
-      <c r="P12" s="8"/>
-      <c r="Q12" s="8"/>
-      <c r="R12" s="9" t="str">
+      <c r="C12" s="8">
+        <v>5</v>
+      </c>
+      <c r="D12" s="8">
+        <v>5</v>
+      </c>
+      <c r="E12" s="8">
+        <v>5</v>
+      </c>
+      <c r="F12" s="8">
+        <v>5</v>
+      </c>
+      <c r="G12" s="8">
+        <v>5</v>
+      </c>
+      <c r="H12" s="8">
+        <v>5</v>
+      </c>
+      <c r="I12" s="8">
+        <v>5</v>
+      </c>
+      <c r="J12" s="8">
+        <v>5</v>
+      </c>
+      <c r="K12" s="8">
+        <v>5</v>
+      </c>
+      <c r="L12" s="8">
+        <v>5</v>
+      </c>
+      <c r="M12" s="8">
+        <v>5</v>
+      </c>
+      <c r="N12" s="8">
+        <v>5</v>
+      </c>
+      <c r="O12" s="8">
+        <v>5</v>
+      </c>
+      <c r="P12" s="8">
+        <v>4</v>
+      </c>
+      <c r="Q12" s="8">
+        <v>5</v>
+      </c>
+      <c r="R12" s="9">
         <f>IF(COUNT(C12:Q12)=0,"",AVERAGE(C12:Q12))</f>
-        <v/>
-      </c>
-      <c r="S12" s="10"/>
-      <c r="T12" s="10"/>
+        <v>4.9333333333333336</v>
+      </c>
+      <c r="S12" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="T12" s="10" t="s">
+        <v>70</v>
+      </c>
       <c r="U12" s="10"/>
       <c r="V12" s="10"/>
     </row>
-    <row r="13" spans="1:22" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:22" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>2</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="11"/>
-      <c r="K13" s="11"/>
-      <c r="L13" s="11"/>
-      <c r="M13" s="11"/>
-      <c r="N13" s="11"/>
-      <c r="O13" s="11"/>
-      <c r="P13" s="11"/>
-      <c r="Q13" s="11"/>
-      <c r="R13" s="9" t="str">
+      <c r="C13" s="11">
+        <v>5</v>
+      </c>
+      <c r="D13" s="11">
+        <v>5</v>
+      </c>
+      <c r="E13" s="11">
+        <v>5</v>
+      </c>
+      <c r="F13" s="11">
+        <v>5</v>
+      </c>
+      <c r="G13" s="11">
+        <v>5</v>
+      </c>
+      <c r="H13" s="11">
+        <v>5</v>
+      </c>
+      <c r="I13" s="11">
+        <v>5</v>
+      </c>
+      <c r="J13" s="11">
+        <v>5</v>
+      </c>
+      <c r="K13" s="11">
+        <v>5</v>
+      </c>
+      <c r="L13" s="11">
+        <v>5</v>
+      </c>
+      <c r="M13" s="11">
+        <v>5</v>
+      </c>
+      <c r="N13" s="11">
+        <v>5</v>
+      </c>
+      <c r="O13" s="11">
+        <v>4</v>
+      </c>
+      <c r="P13" s="11">
+        <v>5</v>
+      </c>
+      <c r="Q13" s="11">
+        <v>5</v>
+      </c>
+      <c r="R13" s="9">
         <f>IF(COUNT(C13:Q13)=0,"",AVERAGE(C13:Q13))</f>
-        <v/>
-      </c>
-      <c r="S13" s="12"/>
-      <c r="T13" s="12"/>
-      <c r="U13" s="12"/>
-      <c r="V13" s="12"/>
-    </row>
-    <row r="14" spans="1:22" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+        <v>4.9333333333333336</v>
+      </c>
+      <c r="S13" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="T13" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="U13" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="V13" s="12" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <v>3</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="8"/>
-      <c r="K14" s="8"/>
-      <c r="L14" s="8"/>
-      <c r="M14" s="8"/>
-      <c r="N14" s="8"/>
-      <c r="O14" s="8"/>
-      <c r="P14" s="8"/>
-      <c r="Q14" s="8"/>
-      <c r="R14" s="9" t="str">
+      <c r="C14" s="8">
+        <v>3</v>
+      </c>
+      <c r="D14" s="8">
+        <v>2</v>
+      </c>
+      <c r="E14" s="8">
+        <v>1</v>
+      </c>
+      <c r="F14" s="8">
+        <v>3</v>
+      </c>
+      <c r="G14" s="8">
+        <v>1</v>
+      </c>
+      <c r="H14" s="8">
+        <v>1</v>
+      </c>
+      <c r="I14" s="8">
+        <v>1</v>
+      </c>
+      <c r="J14" s="8">
+        <v>3</v>
+      </c>
+      <c r="K14" s="8">
+        <v>2</v>
+      </c>
+      <c r="L14" s="8">
+        <v>3</v>
+      </c>
+      <c r="M14" s="8">
+        <v>4</v>
+      </c>
+      <c r="N14" s="8">
+        <v>1</v>
+      </c>
+      <c r="O14" s="8">
+        <v>1</v>
+      </c>
+      <c r="P14" s="8">
+        <v>4</v>
+      </c>
+      <c r="Q14" s="8">
+        <v>2</v>
+      </c>
+      <c r="R14" s="9">
         <f>IF(COUNT(C14:Q14)=0,"",AVERAGE(C14:Q14))</f>
-        <v/>
-      </c>
-      <c r="S14" s="10"/>
-      <c r="T14" s="10"/>
-      <c r="U14" s="10"/>
-      <c r="V14" s="10"/>
-    </row>
-    <row r="15" spans="1:22" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+        <v>2.1333333333333333</v>
+      </c>
+      <c r="S14" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="T14" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="U14" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="V14" s="10" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>4</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-      <c r="I15" s="11"/>
-      <c r="J15" s="11"/>
-      <c r="K15" s="11"/>
-      <c r="L15" s="11"/>
-      <c r="M15" s="11"/>
-      <c r="N15" s="11"/>
-      <c r="O15" s="11"/>
-      <c r="P15" s="11"/>
-      <c r="Q15" s="11"/>
-      <c r="R15" s="9" t="str">
+      <c r="C15" s="11">
+        <v>4</v>
+      </c>
+      <c r="D15" s="11">
+        <v>5</v>
+      </c>
+      <c r="E15" s="11">
+        <v>4</v>
+      </c>
+      <c r="F15" s="11">
+        <v>5</v>
+      </c>
+      <c r="G15" s="11">
+        <v>5</v>
+      </c>
+      <c r="H15" s="11">
+        <v>3</v>
+      </c>
+      <c r="I15" s="11">
+        <v>5</v>
+      </c>
+      <c r="J15" s="11">
+        <v>5</v>
+      </c>
+      <c r="K15" s="11">
+        <v>5</v>
+      </c>
+      <c r="L15" s="11">
+        <v>4</v>
+      </c>
+      <c r="M15" s="11">
+        <v>5</v>
+      </c>
+      <c r="N15" s="11">
+        <v>5</v>
+      </c>
+      <c r="O15" s="11">
+        <v>1</v>
+      </c>
+      <c r="P15" s="11">
+        <v>5</v>
+      </c>
+      <c r="Q15" s="11">
+        <v>5</v>
+      </c>
+      <c r="R15" s="9">
         <f>IF(COUNT(C15:Q15)=0,"",AVERAGE(C15:Q15))</f>
-        <v/>
-      </c>
-      <c r="S15" s="12"/>
-      <c r="T15" s="12"/>
-      <c r="U15" s="12"/>
-      <c r="V15" s="12"/>
-    </row>
-    <row r="16" spans="1:22" ht="48" customHeight="1" x14ac:dyDescent="0.2">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="S15" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="T15" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="U15" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="V15" s="12" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" ht="48" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <v>5</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
-      <c r="I16" s="8"/>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8"/>
-      <c r="L16" s="8"/>
-      <c r="M16" s="8"/>
-      <c r="N16" s="8"/>
-      <c r="O16" s="8"/>
-      <c r="P16" s="8"/>
-      <c r="Q16" s="8"/>
-      <c r="R16" s="9" t="str">
+      <c r="C16" s="8">
+        <v>2</v>
+      </c>
+      <c r="D16" s="8">
+        <v>2</v>
+      </c>
+      <c r="E16" s="8">
+        <v>1</v>
+      </c>
+      <c r="F16" s="8">
+        <v>4</v>
+      </c>
+      <c r="G16" s="8">
+        <v>3</v>
+      </c>
+      <c r="H16" s="8">
+        <v>1</v>
+      </c>
+      <c r="I16" s="8">
+        <v>1</v>
+      </c>
+      <c r="J16" s="8">
+        <v>3</v>
+      </c>
+      <c r="K16" s="8">
+        <v>2</v>
+      </c>
+      <c r="L16" s="8">
+        <v>1</v>
+      </c>
+      <c r="M16" s="8">
+        <v>4</v>
+      </c>
+      <c r="N16" s="8">
+        <v>3</v>
+      </c>
+      <c r="O16" s="8">
+        <v>1</v>
+      </c>
+      <c r="P16" s="8">
+        <v>4</v>
+      </c>
+      <c r="Q16" s="8">
+        <v>2</v>
+      </c>
+      <c r="R16" s="9">
         <f>IF(COUNT(C16:Q16)=0,"",AVERAGE(C16:Q16))</f>
-        <v/>
-      </c>
-      <c r="S16" s="10"/>
-      <c r="T16" s="10"/>
-      <c r="U16" s="10"/>
+        <v>2.2666666666666666</v>
+      </c>
+      <c r="S16" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="T16" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="U16" s="10" t="s">
+        <v>75</v>
+      </c>
       <c r="V16" s="10"/>
     </row>
   </sheetData>
@@ -1224,35 +1450,35 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C27"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="95" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="28" t="s">
         <v>41</v>
       </c>
       <c r="B1" s="23"/>
       <c r="C1" s="23"/>
     </row>
-    <row r="2" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="23"/>
       <c r="C2" s="23"/>
     </row>
-    <row r="3" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="23"/>
       <c r="C3" s="23"/>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>15</v>
       </c>
@@ -1263,7 +1489,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="13">
         <v>1</v>
       </c>
@@ -1274,7 +1500,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="16">
         <v>2</v>
       </c>
@@ -1285,7 +1511,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="13">
         <v>3</v>
       </c>
@@ -1296,7 +1522,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="16">
         <v>4</v>
       </c>
@@ -1307,7 +1533,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="28" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A10" s="13">
         <v>5</v>
       </c>
@@ -1318,7 +1544,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="16">
         <v>6</v>
       </c>
@@ -1329,7 +1555,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="13">
         <v>7</v>
       </c>
@@ -1340,7 +1566,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="16">
         <v>8</v>
       </c>
@@ -1351,7 +1577,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="13">
         <v>9</v>
       </c>
@@ -1362,7 +1588,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="16">
         <v>10</v>
       </c>
@@ -1373,7 +1599,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="28" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A16" s="13">
         <v>11</v>
       </c>
@@ -1384,7 +1610,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="16">
         <v>12</v>
       </c>
@@ -1395,7 +1621,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="13">
         <v>13</v>
       </c>
@@ -1406,7 +1632,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="16">
         <v>14</v>
       </c>
@@ -1417,7 +1643,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="13">
         <v>15</v>
       </c>
@@ -1428,12 +1654,12 @@
         <v>58</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B22" s="19" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B23" s="20">
         <v>1</v>
       </c>
@@ -1441,7 +1667,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B24" s="20">
         <v>2</v>
       </c>
@@ -1449,7 +1675,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B25" s="20">
         <v>3</v>
       </c>
@@ -1457,7 +1683,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B26" s="20">
         <v>4</v>
       </c>
@@ -1465,7 +1691,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B27" s="20">
         <v>5</v>
       </c>
